--- a/loan_approval_output.xlsx
+++ b/loan_approval_output.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -47,16 +50,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,13 +67,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -445,7 +454,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -456,7 +465,7 @@
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="33" customWidth="1" min="16" max="16"/>
@@ -559,44 +568,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Aayush Dev</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>850000</v>
+        <v>797379</v>
       </c>
       <c r="E2" t="n">
-        <v>742</v>
+        <v>690</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>300000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50000</v>
+        <v>240711</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -606,25 +615,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.928</v>
+        <v>0.638</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -633,44 +642,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Sara Khan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1200000</v>
+        <v>1126776</v>
       </c>
       <c r="E3" t="n">
-        <v>780</v>
+        <v>701</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>800000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>100000</v>
+        <v>147972</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+        <v>0.13</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -680,25 +689,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
+        <v>0.794</v>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -707,72 +716,72 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rohan Mehta</t>
+          <t>Manish Tiwari</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>350000</v>
+        <v>956357</v>
       </c>
       <c r="E4" t="n">
-        <v>610</v>
+        <v>667</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>500000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>80000</v>
+        <v>86508</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.43</v>
+        <v>0.52</v>
       </c>
       <c r="J4" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Credit score too low</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+        <v>0.822</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -781,44 +790,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sneha Iyer</t>
+          <t>Sneha K.C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1500000</v>
+        <v>874183</v>
       </c>
       <c r="E5" t="n">
-        <v>810</v>
+        <v>693</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2500000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>200000</v>
+        <v>218560</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+        <v>0.25</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -828,25 +837,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
+        <v>0.86</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -855,44 +864,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>C005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vishal Singh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600000</v>
+        <v>1256699</v>
       </c>
       <c r="E6" t="n">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1800000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>150000</v>
+        <v>128931</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -904,32 +913,32 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.449</v>
+        <v>0.888</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
           <t>No</t>
         </is>
       </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>C006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -938,35 +947,35 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>450000</v>
+        <v>1423525</v>
       </c>
       <c r="E7" t="n">
-        <v>655</v>
+        <v>709</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1500000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>100000</v>
+        <v>338883</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.33</v>
+        <v>1.05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -978,32 +987,32 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.195</v>
+        <v>0.767</v>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A007</t>
+          <t>C007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1012,63 +1021,63 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>900000</v>
+        <v>1682546</v>
       </c>
       <c r="E8" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>700000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>300000</v>
+        <v>419150</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="J8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Credit score too low</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
+        <v>0.962</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1077,7 +1086,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>C008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1086,35 +1095,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>720000</v>
+        <v>1320492</v>
       </c>
       <c r="E9" t="n">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2000000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>90000</v>
+        <v>72928</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+        <v>0.06</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1124,25 +1133,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
+        <v>0.726</v>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1151,72 +1160,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A009</t>
+          <t>C009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Melania Gomes</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>280000</v>
+        <v>965047</v>
       </c>
       <c r="E10" t="n">
-        <v>640</v>
+        <v>674</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>400000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20000</v>
+        <v>109065</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>1.43</v>
+        <v>0.41</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Income too low; Credit score too low</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
+        <v>0.819</v>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1225,44 +1234,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A010</t>
+          <t>C010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Divya Kulkarni</t>
+          <t>Divyanka Kulkarni</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1000000</v>
+        <v>1427517</v>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>726</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>3000000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>400000</v>
+        <v>164322</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+        <v>0.12</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1272,25 +1281,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1299,7 +1308,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A011</t>
+          <t>C011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,63 +1317,63 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>550000</v>
+        <v>1057549</v>
       </c>
       <c r="E12" t="n">
-        <v>705</v>
+        <v>666</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>3500000</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>120000</v>
+        <v>461895</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>6.36</v>
+        <v>3.31</v>
       </c>
       <c r="J12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Loan too large vs income</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
+        <v>0.957</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1373,72 +1382,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A012</t>
+          <t>C012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neha Verma</t>
+          <t>Jayalakshmi Verma</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>780000</v>
+        <v>1546198</v>
       </c>
       <c r="E13" t="n">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1200000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>450000</v>
+        <v>345990</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.54</v>
+        <v>0.78</v>
       </c>
       <c r="J13" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Existing debt too high</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
+        <v>0.835</v>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1447,81 +1456,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A013</t>
+          <t>C013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rahul Desai</t>
+          <t>Huzaifa Desai</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1800000</v>
+        <v>730557</v>
       </c>
       <c r="E14" t="n">
-        <v>790</v>
+        <v>683</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>4000000</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>500000</v>
+        <v>227828</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>2.22</v>
+        <v>5.48</v>
       </c>
       <c r="J14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+        <v>0.31</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>All rules passed</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+          <t>Loan too large vs income</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.983</v>
+        <v>0.969</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A014</t>
+          <t>C014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1530,72 +1539,72 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>500000</v>
+        <v>719017</v>
       </c>
       <c r="E15" t="n">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>900000</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>60000</v>
+        <v>394912</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.12</v>
+        <v>0.55</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
           <t>Rejected</t>
         </is>
       </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Employment too short</t>
+          <t>Existing debt too high</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.587</v>
+        <v>0.418</v>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A015</t>
+          <t>C015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1604,63 +1613,63 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>950000</v>
+        <v>1088398</v>
       </c>
       <c r="E16" t="n">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1000000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>100000</v>
+        <v>135410</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="J16" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Credit score too low</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
+        <v>0.864</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1669,7 +1678,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A016</t>
+          <t>C016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1678,35 +1687,35 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>400000</v>
+        <v>956757</v>
       </c>
       <c r="E17" t="n">
-        <v>720</v>
+        <v>676</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>600000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30000</v>
+        <v>236463</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.63</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1716,25 +1725,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
+        <v>0.775</v>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1743,44 +1752,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A017</t>
+          <t>C017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manish Tiwari</t>
+          <t>Rohan Mehta</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>650000</v>
+        <v>1645719</v>
       </c>
       <c r="E18" t="n">
-        <v>670</v>
+        <v>737</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>2200000</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>200000</v>
+        <v>67589</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>3.38</v>
+        <v>1.34</v>
       </c>
       <c r="J18" t="n">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1792,32 +1801,32 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.482</v>
+        <v>0.641</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
           <t>No</t>
         </is>
       </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A018</t>
+          <t>C018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1826,35 +1835,35 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1100000</v>
+        <v>1209500</v>
       </c>
       <c r="E19" t="n">
-        <v>735</v>
+        <v>677</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1500000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>150000</v>
+        <v>389805</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="J19" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+        <v>0.32</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1864,25 +1873,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
+        <v>0.845</v>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1891,72 +1900,72 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A019</t>
+          <t>C019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nikhil Pandey</t>
+          <t>Aaron Pir</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>320000</v>
+        <v>1149436</v>
       </c>
       <c r="E20" t="n">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1600000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>50000</v>
+        <v>252694</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1.39</v>
       </c>
       <c r="J20" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Loan too large vs income</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
+        <v>0.78</v>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1965,7 +1974,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A020</t>
+          <t>C020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1974,35 +1983,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>880000</v>
+        <v>1006393</v>
       </c>
       <c r="E21" t="n">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>2600000</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>250000</v>
+        <v>182382</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="J21" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -2012,25 +2021,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.522</v>
+        <v>0.824</v>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2083,7 +2092,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2093,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -2103,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2113,7 +2122,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -2133,7 +2142,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -2143,7 +2152,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2185,11 +2194,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit_Score</t>
+          <t>Existing_Debt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.638</v>
+        <v>0.575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2200,26 +2209,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Credit_Score</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.435</v>
+        <v>-0.574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pushes toward Approve</t>
+          <t>Pushes toward Reject</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Loan_to_Income</t>
+          <t>Debt_to_Income</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.382</v>
+        <v>-0.57</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2230,11 +2239,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Employment_Years</t>
+          <t>Loan_to_Income</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.352</v>
+        <v>0.447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2245,26 +2254,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Debt_to_Income</t>
+          <t>Loan_Amount</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.291</v>
+        <v>0.348</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pushes toward Reject</t>
+          <t>Pushes toward Approve</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Existing_Debt</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.268</v>
+        <v>-0.282</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2275,15 +2284,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Loan_Amount</t>
+          <t>Employment_Years</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06</v>
+        <v>0.166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pushes toward Reject</t>
+          <t>Pushes toward Approve</t>
         </is>
       </c>
     </row>
@@ -2294,11 +2303,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06</v>
+        <v>0.157</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pushes toward Reject</t>
+          <t>Pushes toward Approve</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2354,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2360,7 +2369,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300000</v>
+        <v>700000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/loan_approval_output.xlsx
+++ b/loan_approval_output.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -47,16 +50,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,13 +67,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -445,7 +454,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -456,7 +465,7 @@
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="33" customWidth="1" min="16" max="16"/>
@@ -559,72 +568,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Ethan Parker</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>850000</v>
+        <v>759269</v>
       </c>
       <c r="E2" t="n">
-        <v>742</v>
+        <v>518</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>300000</v>
+        <v>2340086</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50000</v>
+        <v>185000</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>0.35</v>
+        <v>3.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
+        <v>0.021</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -633,44 +642,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Olivia Bennett</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1200000</v>
+        <v>1159555</v>
       </c>
       <c r="E3" t="n">
-        <v>780</v>
+        <v>719</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>800000</v>
+        <v>2467713</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>100000</v>
+        <v>35000</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.67</v>
+        <v>2.13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+        <v>0.03</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -680,25 +689,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
+        <v>0.799</v>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -707,72 +716,72 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rohan Mehta</t>
+          <t>Liam Anderson</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>350000</v>
+        <v>1654341</v>
       </c>
       <c r="E4" t="n">
-        <v>610</v>
+        <v>338</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>500000</v>
+        <v>1127739</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>80000</v>
+        <v>270000</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>1.43</v>
+        <v>0.68</v>
       </c>
       <c r="J4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+        <v>0.16</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Credit score too low</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+          <t>Age too low; Credit score too low</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+        <v>0.067</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -781,44 +790,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sneha Iyer</t>
+          <t>Sophie Collins</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1500000</v>
+        <v>1526491</v>
       </c>
       <c r="E5" t="n">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2500000</v>
+        <v>888464</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>200000</v>
+        <v>95000</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>0.58</v>
       </c>
       <c r="J5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+        <v>0.06</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -828,25 +837,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -855,72 +864,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>James Harrison</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600000</v>
+        <v>1019850</v>
       </c>
       <c r="E6" t="n">
-        <v>690</v>
+        <v>751</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1800000</v>
+        <v>3639741</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>150000</v>
+        <v>115000</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.449</v>
+        <v>0.041</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -929,48 +938,48 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ananya Rao</t>
+          <t>Emma Wilson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>450000</v>
+        <v>1417430</v>
       </c>
       <c r="E7" t="n">
-        <v>655</v>
+        <v>687</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1500000</v>
+        <v>563486</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>100000</v>
+        <v>45000</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.33</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.22</v>
+        <v>0.03</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
           <t>Approved</t>
         </is>
       </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>All rules passed</t>
@@ -978,97 +987,97 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.195</v>
+        <v>0.892</v>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A007</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Karan Joshi</t>
+          <t>Noah Mitchell</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>900000</v>
+        <v>524836</v>
       </c>
       <c r="E8" t="n">
-        <v>580</v>
+        <v>367</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>700000</v>
+        <v>1499928</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>300000</v>
+        <v>325000</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.78</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+        <v>0.62</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Credit score too low</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+          <t>Credit score too low; Existing debt too high</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
+        <v>0.002</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1077,44 +1086,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>B008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meera Nair</t>
+          <t>Chloe Thompson</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>720000</v>
+        <v>1475053</v>
       </c>
       <c r="E9" t="n">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2000000</v>
+        <v>443430</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+        <v>0.05</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -1124,25 +1133,25 @@
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
+        <v>0.916</v>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1151,72 +1160,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A009</t>
+          <t>B009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Lucas Morgan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>280000</v>
+        <v>745004</v>
       </c>
       <c r="E10" t="n">
-        <v>640</v>
+        <v>576</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>400000</v>
+        <v>3509251</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20000</v>
+        <v>215000</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.43</v>
+        <v>4.71</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+        <v>0.29</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Income too low; Credit score too low</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
+          <t>Credit score too low; Loan too large vs income</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
+        <v>0.04</v>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1225,72 +1234,72 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A010</t>
+          <t>B010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Divya Kulkarni</t>
+          <t>Grace Williams</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1000000</v>
+        <v>1964547</v>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>348</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3000000</v>
+        <v>2167577</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>400000</v>
+        <v>25000</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
+        <v>0.105</v>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1299,72 +1308,72 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A011</t>
+          <t>B011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siddharth Gupta</t>
+          <t>Daniel Cooper</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>550000</v>
+        <v>1082882</v>
       </c>
       <c r="E12" t="n">
-        <v>705</v>
+        <v>727</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3500000</v>
+        <v>1903556</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>120000</v>
+        <v>160000</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>6.36</v>
+        <v>1.76</v>
       </c>
       <c r="J12" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Loan too large vs income</t>
+          <t>All rules passed</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
+        <v>0.538</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1373,72 +1382,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A012</t>
+          <t>B012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neha Verma</t>
+          <t>Ella Richardson</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>780000</v>
+        <v>1160939</v>
       </c>
       <c r="E13" t="n">
-        <v>668</v>
+        <v>614</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1200000</v>
+        <v>2655769</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="J13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+        <v>0.26</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Existing debt too high</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
+          <t>Credit score too low</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
+        <v>0.035</v>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1447,72 +1456,72 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A013</t>
+          <t>B013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rahul Desai</t>
+          <t>Henry Walker</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1800000</v>
+        <v>543702</v>
       </c>
       <c r="E14" t="n">
-        <v>790</v>
+        <v>683</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4000000</v>
+        <v>2842565</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>500000</v>
+        <v>55000</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>2.22</v>
+        <v>5.23</v>
       </c>
       <c r="J14" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Loan too large vs income</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
+        <v>0.102</v>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1521,118 +1530,118 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A014</t>
+          <t>B014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pooja Bhat</t>
+          <t>Amelia Carter</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1021319</v>
+      </c>
+      <c r="E15" t="n">
+        <v>618</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2809129</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H15" t="n">
         <v>27</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>695</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>900000</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Employment too short</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.587</v>
+        <v>0.028</v>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A015</t>
+          <t>B015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aditya Kapoor</t>
+          <t>Benjamin Brooks</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>950000</v>
+        <v>1255235</v>
       </c>
       <c r="E16" t="n">
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1000000</v>
+        <v>1771225</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>100000</v>
+        <v>285000</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="J16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+        <v>0.23</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -1642,25 +1651,25 @@
           <t>Credit score too low</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
+        <v>0.19</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1669,72 +1678,72 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A016</t>
+          <t>B016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ishita Menon</t>
+          <t>Lily Edwards</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>400000</v>
+        <v>914528</v>
       </c>
       <c r="E17" t="n">
-        <v>720</v>
+        <v>568</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>600000</v>
+        <v>3540266</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>3.87</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
+        <v>0.03</v>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1743,72 +1752,72 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A017</t>
+          <t>B017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manish Tiwari</t>
+          <t>Jack Foster</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>650000</v>
+        <v>1083365</v>
       </c>
       <c r="E18" t="n">
-        <v>670</v>
+        <v>728</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2200000</v>
+        <v>3518100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>200000</v>
+        <v>105000</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I18" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>All rules passed</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.482</v>
+        <v>0.079</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1817,72 +1826,72 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A018</t>
+          <t>B018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kavya Shetty</t>
+          <t>Charlotte Murphy</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1100000</v>
+        <v>821103</v>
       </c>
       <c r="E19" t="n">
-        <v>735</v>
+        <v>471</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1500000</v>
+        <v>2233457</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>150000</v>
+        <v>240000</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>1.36</v>
+        <v>2.72</v>
       </c>
       <c r="J19" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
+        <v>0.019</v>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1891,72 +1900,72 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A019</t>
+          <t>B019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nikhil Pandey</t>
+          <t>Alexander Reed</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>320000</v>
+        <v>1330626</v>
       </c>
       <c r="E20" t="n">
-        <v>660</v>
+        <v>340</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1600000</v>
+        <v>1403993</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1.06</v>
       </c>
       <c r="J20" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
+        <v>0.01</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Loan too large vs income</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
+          <t>Credit score too low</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
+        <v>0.126</v>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1965,72 +1974,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A020</t>
+          <t>B020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tanvi Choudhary</t>
+          <t>Mia Sullivan</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>880000</v>
+        <v>1117358</v>
       </c>
       <c r="E21" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2600000</v>
+        <v>3807519</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>250000</v>
+        <v>340000</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="J21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>All rules passed</t>
+          <t>Credit score too low</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.522</v>
+        <v>0.028</v>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2083,7 +2092,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2093,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2103,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2113,7 +2122,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -2123,7 +2132,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -2133,7 +2142,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -2143,7 +2152,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2189,7 +2198,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.638</v>
+        <v>1.189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2200,26 +2209,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Employment_Years</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.435</v>
+        <v>-0.849</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pushes toward Approve</t>
+          <t>Pushes toward Reject</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Loan_to_Income</t>
+          <t>Loan_Amount</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.382</v>
+        <v>-0.612</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2230,26 +2239,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Employment_Years</t>
+          <t>Loan_to_Income</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.352</v>
+        <v>-0.597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pushes toward Approve</t>
+          <t>Pushes toward Reject</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Debt_to_Income</t>
+          <t>Existing_Debt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.291</v>
+        <v>-0.401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2260,11 +2269,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Existing_Debt</t>
+          <t>Debt_to_Income</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.268</v>
+        <v>-0.292</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2275,11 +2284,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Loan_Amount</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06</v>
+        <v>-0.077</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2294,11 +2303,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.06</v>
+        <v>0.005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pushes toward Reject</t>
+          <t>Pushes toward Approve</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2369,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2390,7 +2399,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
